--- a/database/event/5469/event_5469_evp_summary.xlsx
+++ b/database/event/5469/event_5469_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.7013</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7987</v>
+        <v>3.7179</v>
       </c>
       <c r="E2" t="n">
         <v>10.4463</v>
@@ -548,7 +548,7 @@
         <v>3.8199</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4061</v>
+        <v>2.3445</v>
       </c>
       <c r="E3" t="n">
         <v>6.9991</v>
@@ -594,7 +594,7 @@
         <v>3.7905</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3843</v>
+        <v>2.3231</v>
       </c>
       <c r="E4" t="n">
         <v>6.9452</v>
@@ -640,7 +640,7 @@
         <v>2.9359</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7518</v>
+        <v>1.6992</v>
       </c>
       <c r="E5" t="n">
         <v>5.3794</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0379</v>
+        <v>5.0261</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7495</v>
+        <v>2.7431</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6138</v>
+        <v>1.5585</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0379</v>
+        <v>5.0261</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1646</v>
+        <v>3.1528</v>
       </c>
       <c r="G6" t="n">
         <v>1.8734</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1646</v>
+        <v>3.1528</v>
       </c>
       <c r="I6" t="n">
         <v>3.1793</v>
@@ -732,7 +732,7 @@
         <v>2.6217</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5192</v>
+        <v>1.4698</v>
       </c>
       <c r="E7" t="n">
         <v>4.8036</v>
@@ -778,7 +778,7 @@
         <v>2.5879</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4942</v>
+        <v>1.4452</v>
       </c>
       <c r="E8" t="n">
         <v>4.7418</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3203</v>
+        <v>4.3092</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3579</v>
+        <v>2.3518</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3239</v>
+        <v>1.2729</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3203</v>
+        <v>4.3092</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4564</v>
+        <v>4.4453</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1361</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6846</v>
+        <v>4.6671</v>
       </c>
       <c r="I9" t="n">
         <v>4.7064</v>
@@ -870,7 +870,7 @@
         <v>2.3003</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2813</v>
+        <v>1.2353</v>
       </c>
       <c r="E10" t="n">
         <v>4.2148</v>
@@ -916,7 +916,7 @@
         <v>2.2872</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2716</v>
+        <v>1.2257</v>
       </c>
       <c r="E11" t="n">
         <v>4.1907</v>
@@ -962,7 +962,7 @@
         <v>2.2727</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2609</v>
+        <v>1.2151</v>
       </c>
       <c r="E12" t="n">
         <v>4.1642</v>
@@ -1008,7 +1008,7 @@
         <v>2.2079</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2129</v>
+        <v>1.1678</v>
       </c>
       <c r="E13" t="n">
         <v>4.0454</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.46</v>
+        <v>3.4465</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8884</v>
+        <v>1.881</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9764</v>
+        <v>0.9292</v>
       </c>
       <c r="E14" t="n">
-        <v>3.46</v>
+        <v>3.4465</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6159</v>
+        <v>3.6024</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1559</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6159</v>
+        <v>3.6024</v>
       </c>
       <c r="I14" t="n">
         <v>3.6327</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3803</v>
+        <v>3.3686</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8449</v>
+        <v>1.8385</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9442</v>
+        <v>0.8981</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3803</v>
+        <v>3.3686</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1225</v>
+        <v>3.1108</v>
       </c>
       <c r="G15" t="n">
         <v>0.2578</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1225</v>
+        <v>3.1108</v>
       </c>
       <c r="I15" t="n">
         <v>3.137</v>
@@ -1146,7 +1146,7 @@
         <v>1.7345</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8625</v>
+        <v>0.8222</v>
       </c>
       <c r="E16" t="n">
         <v>3.1781</v>
@@ -1192,7 +1192,7 @@
         <v>1.7324</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8609</v>
+        <v>0.8207</v>
       </c>
       <c r="E17" t="n">
         <v>3.1742</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8146</v>
+        <v>2.8034</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5361</v>
+        <v>1.53</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7157</v>
+        <v>0.673</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8146</v>
+        <v>2.8034</v>
       </c>
       <c r="F18" t="n">
-        <v>3.004</v>
+        <v>2.9928</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1894</v>
       </c>
       <c r="H18" t="n">
-        <v>3.004</v>
+        <v>2.9928</v>
       </c>
       <c r="I18" t="n">
         <v>3.018</v>
@@ -1284,7 +1284,7 @@
         <v>1.4659</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6637</v>
+        <v>0.6262</v>
       </c>
       <c r="E19" t="n">
         <v>2.6859</v>
@@ -1330,7 +1330,7 @@
         <v>1.3433</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5729</v>
+        <v>0.5367</v>
       </c>
       <c r="E20" t="n">
         <v>2.4613</v>
@@ -1376,7 +1376,7 @@
         <v>1.2705</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5191</v>
+        <v>0.4835</v>
       </c>
       <c r="E21" t="n">
         <v>2.3279</v>
@@ -1422,7 +1422,7 @@
         <v>1.2272</v>
       </c>
       <c r="D22" t="n">
-        <v>0.487</v>
+        <v>0.4519</v>
       </c>
       <c r="E22" t="n">
         <v>2.2486</v>
@@ -1468,7 +1468,7 @@
         <v>1.073</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3729</v>
+        <v>0.3393</v>
       </c>
       <c r="E23" t="n">
         <v>1.966</v>
@@ -1514,7 +1514,7 @@
         <v>1.0551</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3596</v>
+        <v>0.3263</v>
       </c>
       <c r="E24" t="n">
         <v>1.9332</v>
@@ -1560,7 +1560,7 @@
         <v>1.0528</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3579</v>
+        <v>0.3246</v>
       </c>
       <c r="E25" t="n">
         <v>1.929</v>
@@ -1606,7 +1606,7 @@
         <v>1.0352</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3449</v>
+        <v>0.3118</v>
       </c>
       <c r="E26" t="n">
         <v>1.8968</v>
@@ -1652,7 +1652,7 @@
         <v>1.0096</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3259</v>
+        <v>0.2931</v>
       </c>
       <c r="E27" t="n">
         <v>1.8498</v>
@@ -1698,7 +1698,7 @@
         <v>0.9832</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3064</v>
+        <v>0.2738</v>
       </c>
       <c r="E28" t="n">
         <v>1.8015</v>
@@ -1744,7 +1744,7 @@
         <v>0.9788</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3031</v>
+        <v>0.2706</v>
       </c>
       <c r="E29" t="n">
         <v>1.7934</v>
@@ -1790,7 +1790,7 @@
         <v>0.9225</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2615</v>
+        <v>0.2295</v>
       </c>
       <c r="E30" t="n">
         <v>1.6903</v>
@@ -1836,7 +1836,7 @@
         <v>0.9208</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2602</v>
+        <v>0.2283</v>
       </c>
       <c r="E31" t="n">
         <v>1.6872</v>
@@ -1882,7 +1882,7 @@
         <v>0.8227</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1876</v>
+        <v>0.1566</v>
       </c>
       <c r="E32" t="n">
         <v>1.5074</v>
@@ -1928,7 +1928,7 @@
         <v>0.7947</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1669</v>
+        <v>0.1362</v>
       </c>
       <c r="E33" t="n">
         <v>1.4561</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3714</v>
+        <v>1.367</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7461</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1327</v>
+        <v>0.1007</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3714</v>
+        <v>1.367</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1811</v>
+        <v>1.1767</v>
       </c>
       <c r="G34" t="n">
         <v>0.1903</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1811</v>
+        <v>1.1767</v>
       </c>
       <c r="I34" t="n">
         <v>1.1866</v>
@@ -2020,7 +2020,7 @@
         <v>0.487</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0609</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="E35" t="n">
         <v>0.8923</v>
@@ -2066,7 +2066,7 @@
         <v>0.4635</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.1055</v>
       </c>
       <c r="E36" t="n">
         <v>0.8493000000000001</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6522</v>
+        <v>0.6508</v>
       </c>
       <c r="C37" t="n">
-        <v>0.356</v>
+        <v>0.3552</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1579</v>
+        <v>-0.1846</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6522</v>
+        <v>0.6508</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3691</v>
+        <v>0.3677</v>
       </c>
       <c r="G37" t="n">
         <v>0.2831</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3691</v>
+        <v>0.3677</v>
       </c>
       <c r="I37" t="n">
         <v>0.3708</v>
@@ -2158,7 +2158,7 @@
         <v>0.3523</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1606</v>
+        <v>-0.1867</v>
       </c>
       <c r="E38" t="n">
         <v>0.6455</v>
@@ -2204,7 +2204,7 @@
         <v>0.3486</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1633</v>
+        <v>-0.1895</v>
       </c>
       <c r="E39" t="n">
         <v>0.6387</v>
@@ -2250,7 +2250,7 @@
         <v>0.3163</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1872</v>
+        <v>-0.213</v>
       </c>
       <c r="E40" t="n">
         <v>0.5796</v>
@@ -2296,7 +2296,7 @@
         <v>0.3012</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1984</v>
+        <v>-0.2241</v>
       </c>
       <c r="E41" t="n">
         <v>0.5518</v>
@@ -2342,7 +2342,7 @@
         <v>0.2558</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.232</v>
+        <v>-0.2572</v>
       </c>
       <c r="E42" t="n">
         <v>0.4687</v>
@@ -2388,7 +2388,7 @@
         <v>0.255</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2326</v>
+        <v>-0.2577</v>
       </c>
       <c r="E43" t="n">
         <v>0.4673</v>
@@ -2434,7 +2434,7 @@
         <v>0.2114</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2649</v>
+        <v>-0.2896</v>
       </c>
       <c r="E44" t="n">
         <v>0.3873</v>
@@ -2480,7 +2480,7 @@
         <v>0.1045</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.344</v>
+        <v>-0.3677</v>
       </c>
       <c r="E45" t="n">
         <v>0.1914</v>
@@ -2526,7 +2526,7 @@
         <v>-0.0001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4214</v>
+        <v>-0.444</v>
       </c>
       <c r="E46" t="n">
         <v>-0.0001</v>
@@ -2572,7 +2572,7 @@
         <v>-0.0381</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4496</v>
+        <v>-0.4717</v>
       </c>
       <c r="E47" t="n">
         <v>-0.0698</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0517</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4596</v>
+        <v>-0.4816</v>
       </c>
       <c r="E48" t="n">
         <v>-0.09470000000000001</v>
@@ -2664,7 +2664,7 @@
         <v>-0.067</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.471</v>
+        <v>-0.4928</v>
       </c>
       <c r="E49" t="n">
         <v>-0.1228</v>
@@ -2710,7 +2710,7 @@
         <v>-0.08069999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4811</v>
+        <v>-0.5028</v>
       </c>
       <c r="E50" t="n">
         <v>-0.1478</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1207</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5107</v>
+        <v>-0.532</v>
       </c>
       <c r="E51" t="n">
         <v>-0.2212</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1398</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5249</v>
+        <v>-0.546</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2562</v>
@@ -2848,7 +2848,7 @@
         <v>-0.143</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5272</v>
+        <v>-0.5483</v>
       </c>
       <c r="E53" t="n">
         <v>-0.262</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1444</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5283</v>
+        <v>-0.5493</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2646</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2102</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5769</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3851</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2153</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5807</v>
+        <v>-0.601</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3944</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2164</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5815</v>
+        <v>-0.6019</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3965</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2333</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5941</v>
+        <v>-0.6142</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4275</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2345</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5949</v>
+        <v>-0.6151</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4296</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2963</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6407</v>
+        <v>-0.6602</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5429</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3985</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7163</v>
+        <v>-0.7348</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7301</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3991</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7168</v>
+        <v>-0.7352</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7312</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4112</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7257</v>
+        <v>-0.7441</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7534</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4238</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7351</v>
+        <v>-0.7533</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7766</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4684</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7681</v>
+        <v>-0.7859</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8583</v>
@@ -3446,7 +3446,7 @@
         <v>-0.499</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7907</v>
+        <v>-0.8082</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9143</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5002</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7916</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9165</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5759</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8476</v>
+        <v>-0.8643</v>
       </c>
       <c r="E68" t="n">
         <v>-1.0552</v>
@@ -3584,7 +3584,7 @@
         <v>-0.622</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8818</v>
+        <v>-0.898</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1397</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6293</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8872</v>
+        <v>-0.9033</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1531</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7768</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9963</v>
+        <v>-1.011</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4233</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8143</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0241</v>
+        <v>-1.0384</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4921</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9157</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0992</v>
+        <v>-1.1123</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6778</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9167</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0999</v>
+        <v>-1.1131</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6796</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9318</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1111</v>
+        <v>-1.1241</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7074</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9416</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1183</v>
+        <v>-1.1312</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7252</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9876</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1524</v>
+        <v>-1.1648</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8095</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4437</v>
+        <v>-2.4421</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.3337</v>
+        <v>-1.3328</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4086</v>
+        <v>-1.4168</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4437</v>
+        <v>-2.4421</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.4437</v>
+        <v>-0.4421</v>
       </c>
       <c r="G78" t="n">
         <v>-2</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.4437</v>
+        <v>-0.4421</v>
       </c>
       <c r="I78" t="n">
         <v>-0.4458</v>
@@ -4044,7 +4044,7 @@
         <v>-1.5608</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5767</v>
+        <v>-1.5833</v>
       </c>
       <c r="E79" t="n">
         <v>-2.8598</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.0273</v>
+        <v>-3.0195</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6522</v>
+        <v>-1.6479</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6443</v>
+        <v>-1.6469</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.0273</v>
+        <v>-3.0195</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.0884</v>
+        <v>-2.0806</v>
       </c>
       <c r="G80" t="n">
         <v>-0.9389</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.0884</v>
+        <v>-2.0806</v>
       </c>
       <c r="I80" t="n">
         <v>-2.0981</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-5.2097</v>
+        <v>-5.194</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.8433</v>
+        <v>-2.8347</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.526</v>
+        <v>-2.5132</v>
       </c>
       <c r="E81" t="n">
-        <v>-5.2097</v>
+        <v>-5.194</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.2228</v>
+        <v>-4.2071</v>
       </c>
       <c r="G81" t="n">
         <v>-0.9869</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.2228</v>
+        <v>-4.2071</v>
       </c>
       <c r="I81" t="n">
         <v>-4.2425</v>
